--- a/BAP_App_Roster_Prompts_Import.xlsx
+++ b/BAP_App_Roster_Prompts_Import.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -445,7 +445,8 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -491,10 +492,15 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>end_time</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>category</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>surface</t>
         </is>
@@ -533,12 +539,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>profile</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>profile</t>
         </is>
@@ -587,10 +594,15 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
           <t>meal</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
@@ -639,10 +651,15 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>activity</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
